--- a/Assets/07Table/DC.xlsx
+++ b/Assets/07Table/DC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tpgml\Documents\GitHub\DC\Assets\07Table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b1b27ea48e47843/ドキュメント/GitHub/DC/Assets/07Table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F5CC93E-2525-4346-ABFB-9307614E6D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{6F5CC93E-2525-4346-ABFB-9307614E6D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAADA9A2-BDFC-4E38-8A41-742A7D836679}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{FE9215E3-7F1A-4C13-BA27-E6A65D1A04B4}"/>
+    <workbookView xWindow="10485" yWindow="3180" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="9" xr2:uid="{FE9215E3-7F1A-4C13-BA27-E6A65D1A04B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="11" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="ArtifactCombination" sheetId="12" r:id="rId7"/>
     <sheet name="Skill" sheetId="6" r:id="rId8"/>
     <sheet name="Script" sheetId="10" r:id="rId9"/>
+    <sheet name="Chest" sheetId="13" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="439">
   <si>
     <t>Name</t>
     <phoneticPr fontId="16" type="noConversion"/>
@@ -1675,6 +1676,18 @@
   </si>
   <si>
     <t>초록 빛으로 빛나는 보석. 던전에서 드물게 발견되는 듯하다.</t>
+  </si>
+  <si>
+    <t>Golden</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>Silver</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wooden</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2348,6 +2361,115 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FA7155D-0B40-4DCA-B05A-1896C2D3C958}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>35</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>38</v>
+      </c>
+      <c r="D3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>19</v>
+      </c>
+      <c r="C4">
+        <v>41</v>
+      </c>
+      <c r="D4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>21</v>
+      </c>
+      <c r="C5">
+        <v>44</v>
+      </c>
+      <c r="D5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <v>47</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>25</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F2E1B3E-CA27-46A0-860D-0AA4D3F95ADD}">
   <dimension ref="A1:T22"/>
